--- a/Submit/Results/hoangbsthe186345/TC2_Send/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC2_Send/GradeDetail.xlsx
@@ -92,16 +92,16 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: client output matches exactly</x:t>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>ServerStdout</x:t>
@@ -110,30 +110,9 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
     <x:t>Text comparison failed: server output mismatch</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">The command could not be loaded, possibly because:
-  * You intended to execute a .NET application:
-      The application '/apps/Server/Project11.dll' does not exist.
-  * You intended to execute a .NET SDK command:
-      No .NET SDKs were found.
-Download a .NET SDK:
-https://aka.ms/dotnet/download
-Learn about SDK resolution:
-https://aka.ms/dotnet/sdk-not-found
-</x:t>
-  </x:si>
-  <x:si>
     <x:t>Time</x:t>
   </x:si>
   <x:si>
@@ -194,6 +173,9 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
@@ -210,28 +192,6 @@
   </x:si>
   <x:si>
     <x:t>Data transfer in progress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, PSH</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1 + 2
-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, RST</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection reset (RST) - Error occurred</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -258,7 +218,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -267,17 +227,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
+        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -300,7 +250,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -310,14 +260,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -326,19 +270,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -766,19 +698,19 @@
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="9.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13.567768" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16.424911" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.567768" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -869,7 +801,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -907,7 +839,7 @@
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="56.424911" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -977,13 +909,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>0</x:v>
@@ -995,10 +927,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="S2" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="S2" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1031,11 +963,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P9"/>
+  <x:dimension ref="A1:P6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1044,8 +976,8 @@
     <x:col min="8" max="8" width="4.996339" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="10.853482" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1057,49 +989,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="G1" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="H1" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="I1" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="K1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="L1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="M1" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="N1" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="O1" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1110,45 +1042,45 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="J2" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="3" t="s">
+      <x:c r="P2" s="2" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1160,45 +1092,45 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P3" s="3" t="s">
+      <x:c r="P3" s="2" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1210,45 +1142,45 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P4" s="3" t="s">
+      <x:c r="P4" s="2" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1260,46 +1192,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="O5" s="2" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="P5" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P5" s="2" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:16">
@@ -1310,196 +1242,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="4" t="s">
-        <x:v>63</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:16">
-      <x:c r="A7" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="L7" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="M7" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="N7" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="O7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P7" s="5" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:16">
-      <x:c r="A8" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P8" s="5" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:16">
-      <x:c r="A9" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="M9" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P9" s="5" t="s">
-        <x:v>67</x:v>
+      <x:c r="P6" s="2" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/hoangbsthe186345/TC2_Send/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC2_Send/GradeDetail.xlsx
@@ -110,27 +110,10 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: server output mismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">The command could not be loaded, possibly because:
-  * You intended to execute a .NET application:
-      The application '/apps/Server/Project11.dll' does not exist.
-  * You intended to execute a .NET SDK command:
-      No .NET SDKs were found.
-Download a .NET SDK:
-https://aka.ms/dotnet/download
-Learn about SDK resolution:
-https://aka.ms/dotnet/sdk-not-found
+    <x:t>Text comparison passed: server output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Waiting for a connection from client
 </x:t>
   </x:si>
   <x:si>
@@ -229,6 +212,15 @@
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACK, FIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Closing connection (FIN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -880,19 +872,19 @@
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.567768" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.567768" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="56.424911" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -962,13 +954,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>0</x:v>
@@ -980,10 +972,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="S2" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1042,49 +1034,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="F1" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="G1" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="H1" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="I1" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="K1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="L1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="M1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="N1" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="O1" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1095,40 +1087,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
+      <x:c r="J2" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="J2" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="K2" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="M2" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="N2" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1145,40 +1137,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
+      <x:c r="K3" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1195,40 +1187,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="J4" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1245,43 +1237,43 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
+      <x:c r="J5" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="O5" s="2" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="M5" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="N5" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="O5" s="2" t="s">
-        <x:v>62</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1295,40 +1287,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
@@ -1342,7 +1334,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>17</x:v>
@@ -1369,22 +1361,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="M7" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="L7" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="M7" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="N7" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="O7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P7" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1392,49 +1384,49 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1442,7 +1434,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>17</x:v>
@@ -1469,22 +1461,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M9" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P9" s="4" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="M9" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P9" s="4" t="s">
-        <x:v>66</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/hoangbsthe186345/TC2_Send/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC2_Send/GradeDetail.xlsx
@@ -202,25 +202,16 @@
 </x:t>
   </x:si>
   <x:si>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
     <x:t>ACK, RST</x:t>
   </x:si>
   <x:si>
     <x:t>Connection reset (RST) - Error occurred</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, FIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1311,10 +1302,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
         <x:v>51</x:v>
@@ -1334,7 +1325,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>17</x:v>
@@ -1376,7 +1367,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P7" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1384,37 +1375,37 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
         <x:v>51</x:v>
@@ -1426,7 +1417,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1434,37 +1425,37 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
         <x:v>51</x:v>
@@ -1476,7 +1467,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/hoangbsthe186345/TC2_Send/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC2_Send/GradeDetail.xlsx
@@ -92,16 +92,16 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: client output matches exactly</x:t>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>ServerStdout</x:t>
@@ -110,11 +110,7 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t>Text comparison passed: server output matches exactly</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Waiting for a connection from client
-</x:t>
+    <x:t>Text comparison failed: server output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>Time</x:t>
@@ -177,6 +173,9 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
@@ -193,25 +192,6 @@
   </x:si>
   <x:si>
     <x:t>Data transfer in progress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, PSH</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1 + 2
-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, RST</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection reset (RST) - Error occurred</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -238,7 +218,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -247,12 +227,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
+        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -275,7 +250,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="4">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -285,11 +260,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -298,15 +270,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -734,19 +698,19 @@
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="9.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13.567768" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16.424911" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.567768" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -837,7 +801,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -863,19 +827,19 @@
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="9.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13.567768" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16.424911" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.567768" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -965,8 +929,8 @@
       <x:c r="M2" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="S2" s="2" t="s">
-        <x:v>31</x:v>
+      <x:c r="S2" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -999,11 +963,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P9"/>
+  <x:dimension ref="A1:P6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1012,8 +976,8 @@
     <x:col min="8" max="8" width="4.996339" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="10.853482" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1025,49 +989,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="D1" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="E1" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="F1" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="G1" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="H1" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="I1" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="K1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="L1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="M1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="N1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="O1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1078,45 +1042,45 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
+      <x:c r="G2" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="s">
+      <x:c r="H2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
+      <x:c r="J2" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="J2" s="0" t="s">
+      <x:c r="K2" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="3" t="s">
+      <x:c r="P2" s="2" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1128,7 +1092,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1146,27 +1110,27 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P3" s="3" t="s">
+      <x:c r="P3" s="2" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1178,7 +1142,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1196,27 +1160,27 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="J4" s="0" t="s">
+      <x:c r="K4" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P4" s="3" t="s">
+      <x:c r="P4" s="2" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1228,7 +1192,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1246,27 +1210,27 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="J5" s="0" t="s">
+      <x:c r="K5" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="O5" s="2" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="P5" s="3" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P5" s="2" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1278,7 +1242,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1296,178 +1260,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="3" t="s">
+      <x:c r="P6" s="2" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:16">
-      <x:c r="A7" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L7" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="M7" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="N7" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="O7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P7" s="4" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:16">
-      <x:c r="A8" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P8" s="4" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:16">
-      <x:c r="A9" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="M9" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P9" s="4" t="s">
-        <x:v>61</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/hoangbsthe186345/TC2_Send/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC2_Send/GradeDetail.xlsx
@@ -92,106 +92,138 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
+    <x:t>PASS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NONE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison passed: client output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ServerStdout</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Waiting for a connection from client</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison passed: server output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Waiting for a connection from client
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Time</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Info</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Source</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Destination</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Flags</x:t>
+  </x:si>
+  <x:si>
+    <x:t>State</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SourceRole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DestinationRole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ActualFlags</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ActualState</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ActualSourceRole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ActualDestRole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ActualData</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NetworkResult</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Client connecting to server (SYN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Client</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Server</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Server responding (SYN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Connection established</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSH, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data transfer in progress</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1 + 2
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
     <x:t>FAIL</x:t>
   </x:si>
   <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ServerStdout</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Waiting for a connection from client</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: server output mismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Time</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Info</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Source</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Destination</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Flags</x:t>
-  </x:si>
-  <x:si>
-    <x:t>State</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Data</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SourceRole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DestinationRole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ActualFlags</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ActualState</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ActualSourceRole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ActualDestRole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ActualData</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NetworkResult</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Client connecting to server (SYN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Client</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SYN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server responding (SYN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection established</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSH, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Data transfer in progress</x:t>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RST, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Connection reset (RST) - Error occurred</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Closing connection (FIN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -218,7 +250,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -227,7 +259,17 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -250,7 +292,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -260,8 +302,14 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -270,7 +318,19 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -698,19 +758,19 @@
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.567768" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.567768" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -801,7 +861,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -827,19 +887,19 @@
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.567768" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.567768" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -929,8 +989,8 @@
       <x:c r="M2" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="S2" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="S2" s="2" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -963,11 +1023,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P6"/>
+  <x:dimension ref="A1:P10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -977,7 +1037,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -989,49 +1049,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O1" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1042,7 +1102,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1051,36 +1111,36 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
+      <x:c r="L2" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="J2" s="0" t="s">
+      <x:c r="M2" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K2" s="0" t="s">
+      <x:c r="N2" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="2" t="s">
+      <x:c r="P2" s="3" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1092,7 +1152,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1110,27 +1170,27 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="K3" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P3" s="2" t="s">
+      <x:c r="P3" s="3" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1142,7 +1202,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1160,27 +1220,27 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K4" s="0" t="s">
+      <x:c r="N4" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P4" s="2" t="s">
+      <x:c r="P4" s="3" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1192,7 +1252,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1210,27 +1270,27 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K5" s="0" t="s">
+      <x:c r="N5" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P5" s="2" t="s">
+      <x:c r="O5" s="2" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1242,7 +1302,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1260,28 +1320,228 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="J6" s="0" t="s">
+      <x:c r="K6" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P6" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:16">
+      <x:c r="A7" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="K6" s="0" t="s">
+      <x:c r="M7" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P6" s="2" t="s">
-        <x:v>24</x:v>
+      <x:c r="O7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P7" s="5" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:16">
+      <x:c r="A8" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P8" s="5" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:16">
+      <x:c r="A9" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="M9" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P9" s="5" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:16">
+      <x:c r="A10" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P10" s="5" t="s">
+        <x:v>62</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/hoangbsthe186345/TC2_Send/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC2_Send/GradeDetail.xlsx
@@ -92,16 +92,16 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: client output matches exactly</x:t>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>ServerStdout</x:t>
@@ -110,11 +110,7 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t>Text comparison passed: server output matches exactly</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Waiting for a connection from client
-</x:t>
+    <x:t>Text comparison failed: server output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>Time</x:t>
@@ -177,6 +173,9 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
@@ -193,37 +192,6 @@
   </x:si>
   <x:si>
     <x:t>Data transfer in progress</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1 + 2
-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection reset (RST) - Error occurred</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -250,7 +218,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -259,17 +227,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -292,7 +250,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -302,14 +260,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -318,19 +270,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -758,19 +698,19 @@
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="9.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13.567768" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16.424911" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.567768" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -861,7 +801,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -887,19 +827,19 @@
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="9.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13.567768" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16.424911" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.567768" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -989,8 +929,8 @@
       <x:c r="M2" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="S2" s="2" t="s">
-        <x:v>31</x:v>
+      <x:c r="S2" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1023,11 +963,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P10"/>
+  <x:dimension ref="A1:P6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1037,7 +977,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1049,49 +989,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="D1" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="E1" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="F1" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="G1" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="H1" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="I1" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="K1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="L1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="M1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="N1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="O1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1102,45 +1042,45 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
+      <x:c r="G2" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="s">
+      <x:c r="H2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
+      <x:c r="J2" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="J2" s="0" t="s">
+      <x:c r="K2" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="3" t="s">
+      <x:c r="P2" s="2" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1152,7 +1092,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1170,27 +1110,27 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P3" s="3" t="s">
+      <x:c r="P3" s="2" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1202,7 +1142,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1220,27 +1160,27 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="J4" s="0" t="s">
+      <x:c r="K4" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P4" s="3" t="s">
+      <x:c r="P4" s="2" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1252,7 +1192,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1270,27 +1210,27 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="J5" s="0" t="s">
+      <x:c r="K5" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="O5" s="2" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="P5" s="3" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P5" s="2" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1302,7 +1242,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1320,14 +1260,14 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1340,208 +1280,8 @@
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="4" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:16">
-      <x:c r="A7" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L7" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="M7" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="N7" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="O7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P7" s="5" t="s">
-        <x:v>62</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:16">
-      <x:c r="A8" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P8" s="5" t="s">
-        <x:v>62</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:16">
-      <x:c r="A9" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="M9" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P9" s="5" t="s">
-        <x:v>62</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:16">
-      <x:c r="A10" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="M10" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P10" s="5" t="s">
-        <x:v>62</x:v>
+      <x:c r="P6" s="2" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/hoangbsthe186345/TC2_Send/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC2_Send/GradeDetail.xlsx
@@ -92,16 +92,16 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
+    <x:t>PASS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NONE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison passed: client output matches exactly</x:t>
   </x:si>
   <x:si>
     <x:t>ServerStdout</x:t>
@@ -110,7 +110,11 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t>Text comparison failed: server output mismatch</x:t>
+    <x:t>Text comparison passed: server output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Waiting for a connection from client
+</x:t>
   </x:si>
   <x:si>
     <x:t>Time</x:t>
@@ -173,9 +177,6 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
@@ -192,6 +193,22 @@
   </x:si>
   <x:si>
     <x:t>Data transfer in progress</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1 + 2
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RST, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Connection reset (RST) - Error occurred</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -218,7 +235,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -227,7 +244,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
+        <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -250,7 +272,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -260,8 +282,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -270,7 +295,15 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -698,19 +731,19 @@
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.567768" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.567768" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -801,7 +834,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -827,19 +860,19 @@
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.567768" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.567768" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -929,8 +962,8 @@
       <x:c r="M2" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="S2" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="S2" s="2" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -963,11 +996,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P6"/>
+  <x:dimension ref="A1:P9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -976,8 +1009,8 @@
     <x:col min="8" max="8" width="4.996339" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10.853482" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -989,49 +1022,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O1" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1042,7 +1075,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1051,36 +1084,36 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
+      <x:c r="L2" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="J2" s="0" t="s">
+      <x:c r="M2" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K2" s="0" t="s">
+      <x:c r="N2" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="2" t="s">
+      <x:c r="P2" s="3" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1092,7 +1125,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1110,27 +1143,27 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="K3" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P3" s="2" t="s">
+      <x:c r="P3" s="3" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1142,7 +1175,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1160,27 +1193,27 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K4" s="0" t="s">
+      <x:c r="N4" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P4" s="2" t="s">
+      <x:c r="P4" s="3" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1192,7 +1225,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1210,27 +1243,27 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K5" s="0" t="s">
+      <x:c r="N5" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P5" s="2" t="s">
+      <x:c r="O5" s="2" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1242,7 +1275,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1260,28 +1293,178 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="J6" s="0" t="s">
+      <x:c r="K6" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P6" s="3" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:16">
+      <x:c r="A7" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="K6" s="0" t="s">
+      <x:c r="M7" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P6" s="2" t="s">
-        <x:v>24</x:v>
+      <x:c r="O7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P7" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:16">
+      <x:c r="A8" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P8" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:16">
+      <x:c r="A9" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="M9" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P9" s="4" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/hoangbsthe186345/TC2_Send/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC2_Send/GradeDetail.xlsx
@@ -199,16 +199,22 @@
 </x:t>
   </x:si>
   <x:si>
+    <x:t>PARTIAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>(Not validated by this test case)</x:t>
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>RST, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection reset (RST) - Error occurred</x:t>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Closing connection (FIN-ACK)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -235,7 +241,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -245,6 +251,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFF00"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -272,7 +283,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="4">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -285,8 +296,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -304,6 +318,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -996,7 +1014,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P9"/>
+  <x:dimension ref="A1:P19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
@@ -1010,7 +1028,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="10.853482" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1305,16 +1323,16 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="P6" s="4" t="s">
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1322,7 +1340,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>17</x:v>
@@ -1363,8 +1381,8 @@
       <x:c r="O7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P7" s="4" t="s">
-        <x:v>60</x:v>
+      <x:c r="P7" s="5" t="s">
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1372,7 +1390,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>17</x:v>
@@ -1399,22 +1417,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P8" s="5" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P8" s="4" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1422,7 +1440,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>17</x:v>
@@ -1449,22 +1467,522 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M9" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P9" s="5" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="L9" s="0" t="s">
+    </x:row>
+    <x:row r="10" spans="1:16">
+      <x:c r="A10" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="O10" s="2" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="P10" s="5" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:16">
+      <x:c r="A11" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P11" s="5" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:16">
+      <x:c r="A12" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="M9" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P9" s="4" t="s">
+      <x:c r="P12" s="5" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:16">
+      <x:c r="A13" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
         <x:v>60</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M13" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="O13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P13" s="5" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:16">
+      <x:c r="A14" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K14" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="M14" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N14" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O14" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="P14" s="5" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:16">
+      <x:c r="A15" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K15" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L15" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M15" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="N15" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="O15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P15" s="5" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:16">
+      <x:c r="A16" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K16" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="L16" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="M16" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="N16" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="O16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P16" s="5" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:16">
+      <x:c r="A17" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K17" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="L17" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="M17" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="N17" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="O17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P17" s="5" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:16">
+      <x:c r="A18" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K18" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L18" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M18" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N18" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P18" s="5" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:16">
+      <x:c r="A19" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K19" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L19" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M19" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N19" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P19" s="5" t="s">
+        <x:v>61</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
